--- a/Unified_PDF_Platform/unified_outputs/BCBS RI Revival Hotels Feb-25 Inv_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/BCBS RI Revival Hotels Feb-25 Inv_invoice.xlsx
@@ -642,10 +642,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GREGORY D</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>GREGORY</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -671,25 +675,13 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>INVOICE TOTAL</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">

--- a/Unified_PDF_Platform/unified_outputs/BCBS RI Revival Hotels Feb-25 Inv_invoice.xlsx
+++ b/Unified_PDF_Platform/unified_outputs/BCBS RI Revival Hotels Feb-25 Inv_invoice.xlsx
@@ -554,12 +554,18 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>2194.1</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -606,12 +612,18 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>541.3200000000001</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -662,12 +674,18 @@
           <t>MEDICAL</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>MEDICAL</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>566.48</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -681,7 +699,11 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
